--- a/data/samples/web_generated_tasks.xlsx
+++ b/data/samples/web_generated_tasks.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tasks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="tasks" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,53 +454,63 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>expected_old_price</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>target_price</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>target_status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>pricing_source</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>decision_trace</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>result_message</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>required_by</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dfd4af332162</t>
+          <t>4b94e4383226</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SKU-002</t>
+          <t>AISHA-B-60-Z</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>default_platform</t>
+          <t>蚂蚁花团供应商</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>set_offline</t>
+          <t>update_price</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -509,44 +519,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-25T20:34:25.514836+00:00</t>
+          <t>2026-07-22T16:07:33.053595+00:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>26.80</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>set_offline</t>
+          <t>26.90</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>{'listing_trace': ['matched:LIST-LOW:set_offline']}</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>rule_plus_ai</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>{'matched_rule_ids': ['PRICE-0-1'], 'matched_rule_names': ['蚂蚁加价0.1'], 'rule_steps': ['old_price=26.80', 'winning_rule:PRICE-0-1:priority=10:specificity=1', 'rule:PRICE-0-1:fixed_markup-&gt;26.90', 'rule:PRICE-0-1:rounded-&gt;26.90'], 'rule_price': '26.90', 'ai_considered': True, 'ai_suggested_price': '12.74', 'ai_confidence': '0.62', 'ai_reason': 'mock_inventory_sensitivity', 'final_policy': 'rule_price_kept_for_current_stage', 'generation_mode': 'single_rule', 'selected_rule_type': 'price', 'selected_rule_id': 'PRICE-0-1', 'selected_rule_platform_filter': '蚂蚁', 'resolved_platform_name': '蚂蚁花团供应商', 'task_group_id': 'RULE-GROUP-5b8ed8977e8f'}</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-07-23T00:37:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>953006c92dd4</t>
+          <t>d8e8e7c1c49e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SKU-003</t>
+          <t>AISHA-C-55-Z</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>default_platform</t>
+          <t>蚂蚁花团供应商</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>set_offline</t>
+          <t>update_price</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -555,44 +580,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-25T20:34:25.514836+00:00</t>
+          <t>2026-07-22T16:07:33.053595+00:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>13.20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>set_offline</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>{'listing_trace': ['sale_enabled=false-&gt;force_set_offline']}</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>rule_plus_ai</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>{'matched_rule_ids': ['PRICE-0-1'], 'matched_rule_names': ['蚂蚁加价0.1'], 'rule_steps': ['old_price=13.20', 'winning_rule:PRICE-0-1:priority=10:specificity=1', 'rule:PRICE-0-1:fixed_markup-&gt;13.30', 'rule:PRICE-0-1:rounded-&gt;13.30'], 'rule_price': '13.30', 'ai_considered': True, 'ai_suggested_price': '5.15', 'ai_confidence': '0.62', 'ai_reason': 'mock_inventory_sensitivity', 'final_policy': 'rule_price_kept_for_current_stage', 'generation_mode': 'single_rule', 'selected_rule_type': 'price', 'selected_rule_id': 'PRICE-0-1', 'selected_rule_platform_filter': '蚂蚁', 'resolved_platform_name': '蚂蚁花团供应商', 'task_group_id': 'RULE-GROUP-5b8ed8977e8f'}</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-07-23T00:37:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>932296a6a520</t>
+          <t>2005650cd044</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKU-001</t>
+          <t>AISHA-D-50-Z</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>default_platform</t>
+          <t>蚂蚁花团供应商</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>set_online</t>
+          <t>update_price</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -601,35 +641,50 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-25T20:34:25.514836+00:00</t>
+          <t>2026-07-22T16:07:33.054906+00:00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>16.90</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>set_online</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>{'listing_trace': ['matched:LIST-RESTOCK:set_online']}</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>rule_plus_ai</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>{'matched_rule_ids': ['PRICE-0-1'], 'matched_rule_names': ['蚂蚁加价0.1'], 'rule_steps': ['old_price=16.90', 'winning_rule:PRICE-0-1:priority=10:specificity=1', 'rule:PRICE-0-1:fixed_markup-&gt;17.00', 'rule:PRICE-0-1:rounded-&gt;17.00'], 'rule_price': '17.00', 'ai_considered': True, 'ai_suggested_price': '5.15', 'ai_confidence': '0.62', 'ai_reason': 'mock_inventory_sensitivity', 'final_policy': 'rule_price_kept_for_current_stage', 'generation_mode': 'single_rule', 'selected_rule_type': 'price', 'selected_rule_id': 'PRICE-0-1', 'selected_rule_platform_filter': '蚂蚁', 'resolved_platform_name': '蚂蚁花团供应商', 'task_group_id': 'RULE-GROUP-5b8ed8977e8f'}</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-07-23T00:37:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20940412d774</t>
+          <t>cfecda556ebf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKU-001</t>
+          <t>CAPPUCCINO-E-45-Z</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>default_platform</t>
+          <t>蚂蚁花团供应商</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -647,25 +702,35 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-25T20:34:25.514836+00:00</t>
+          <t>2026-07-22T16:07:33.054906+00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+          <t>12.40</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12.50</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>rule_plus_ai</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>{'matched_rule_ids': ['RULE-ALL-1', 'RULE-ROSE-A'], 'matched_rule_names': ['全局固定加价', 'A级品种加价10%'], 'rule_steps': ['base_cost=10', 'rule:RULE-ALL-1:fixed_markup-&gt;15', 'rule:RULE-ALL-1:rounded-&gt;15', 'rule:RULE-ROSE-A:percentage_markup-&gt;16.5', 'rule:RULE-ROSE-A:rounded-&gt;16.5'], 'rule_price': '16.50', 'ai_considered': True, 'ai_suggested_price': '17.64', 'ai_confidence': '0.62', 'ai_reason': 'mock_inventory_sensitivity', 'final_policy': 'rule_price_kept_for_current_stage'}</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>{'matched_rule_ids': ['PRICE-0-1'], 'matched_rule_names': ['蚂蚁加价0.1'], 'rule_steps': ['old_price=12.40', 'winning_rule:PRICE-0-1:priority=10:specificity=1', 'rule:PRICE-0-1:fixed_markup-&gt;12.50', 'rule:PRICE-0-1:rounded-&gt;12.50'], 'rule_price': '12.50', 'ai_considered': True, 'ai_suggested_price': '4.12', 'ai_confidence': '0.62', 'ai_reason': 'mock_inventory_sensitivity', 'final_policy': 'rule_price_kept_for_current_stage', 'generation_mode': 'single_rule', 'selected_rule_type': 'price', 'selected_rule_id': 'PRICE-0-1', 'selected_rule_platform_filter': '蚂蚁', 'resolved_platform_name': '蚂蚁花团供应商', 'task_group_id': 'RULE-GROUP-5b8ed8977e8f'}</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-07-23T00:37:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/samples/web_generated_tasks.xlsx
+++ b/data/samples/web_generated_tasks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,25 +464,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>target_inventory</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>target_status</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>pricing_source</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>decision_trace</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>result_message</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>required_by</t>
         </is>
@@ -491,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4b94e4383226</t>
+          <t>d3425c51151b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,11 +511,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>update_price</t>
+          <t>set_offline</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -519,216 +524,23 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-22T16:07:33.053595+00:00</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>26.80</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>26.90</t>
+          <t>2026-07-27T10:24:22.349670+00:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>rule_plus_ai</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>{'matched_rule_ids': ['PRICE-0-1'], 'matched_rule_names': ['蚂蚁加价0.1'], 'rule_steps': ['old_price=26.80', 'winning_rule:PRICE-0-1:priority=10:specificity=1', 'rule:PRICE-0-1:fixed_markup-&gt;26.90', 'rule:PRICE-0-1:rounded-&gt;26.90'], 'rule_price': '26.90', 'ai_considered': True, 'ai_suggested_price': '12.74', 'ai_confidence': '0.62', 'ai_reason': 'mock_inventory_sensitivity', 'final_policy': 'rule_price_kept_for_current_stage', 'generation_mode': 'single_rule', 'selected_rule_type': 'price', 'selected_rule_id': 'PRICE-0-1', 'selected_rule_platform_filter': '蚂蚁', 'resolved_platform_name': '蚂蚁花团供应商', 'task_group_id': 'RULE-GROUP-5b8ed8977e8f'}</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-07-23T00:37:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>d8e8e7c1c49e</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AISHA-C-55-Z</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>蚂蚁花团供应商</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>update_price</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-07-22T16:07:33.053595+00:00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>13.20</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13.30</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>rule_plus_ai</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>{'matched_rule_ids': ['PRICE-0-1'], 'matched_rule_names': ['蚂蚁加价0.1'], 'rule_steps': ['old_price=13.20', 'winning_rule:PRICE-0-1:priority=10:specificity=1', 'rule:PRICE-0-1:fixed_markup-&gt;13.30', 'rule:PRICE-0-1:rounded-&gt;13.30'], 'rule_price': '13.30', 'ai_considered': True, 'ai_suggested_price': '5.15', 'ai_confidence': '0.62', 'ai_reason': 'mock_inventory_sensitivity', 'final_policy': 'rule_price_kept_for_current_stage', 'generation_mode': 'single_rule', 'selected_rule_type': 'price', 'selected_rule_id': 'PRICE-0-1', 'selected_rule_platform_filter': '蚂蚁', 'resolved_platform_name': '蚂蚁花团供应商', 'task_group_id': 'RULE-GROUP-5b8ed8977e8f'}</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-07-23T00:37:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2005650cd044</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AISHA-D-50-Z</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>蚂蚁花团供应商</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>update_price</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-07-22T16:07:33.054906+00:00</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>16.90</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>rule_plus_ai</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>{'matched_rule_ids': ['PRICE-0-1'], 'matched_rule_names': ['蚂蚁加价0.1'], 'rule_steps': ['old_price=16.90', 'winning_rule:PRICE-0-1:priority=10:specificity=1', 'rule:PRICE-0-1:fixed_markup-&gt;17.00', 'rule:PRICE-0-1:rounded-&gt;17.00'], 'rule_price': '17.00', 'ai_considered': True, 'ai_suggested_price': '5.15', 'ai_confidence': '0.62', 'ai_reason': 'mock_inventory_sensitivity', 'final_policy': 'rule_price_kept_for_current_stage', 'generation_mode': 'single_rule', 'selected_rule_type': 'price', 'selected_rule_id': 'PRICE-0-1', 'selected_rule_platform_filter': '蚂蚁', 'resolved_platform_name': '蚂蚁花团供应商', 'task_group_id': 'RULE-GROUP-5b8ed8977e8f'}</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-07-23T00:37:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cfecda556ebf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CAPPUCCINO-E-45-Z</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>蚂蚁花团供应商</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>update_price</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-07-22T16:07:33.054906+00:00</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>12.40</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12.50</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>rule_plus_ai</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>{'matched_rule_ids': ['PRICE-0-1'], 'matched_rule_names': ['蚂蚁加价0.1'], 'rule_steps': ['old_price=12.40', 'winning_rule:PRICE-0-1:priority=10:specificity=1', 'rule:PRICE-0-1:fixed_markup-&gt;12.50', 'rule:PRICE-0-1:rounded-&gt;12.50'], 'rule_price': '12.50', 'ai_considered': True, 'ai_suggested_price': '4.12', 'ai_confidence': '0.62', 'ai_reason': 'mock_inventory_sensitivity', 'final_policy': 'rule_price_kept_for_current_stage', 'generation_mode': 'single_rule', 'selected_rule_type': 'price', 'selected_rule_id': 'PRICE-0-1', 'selected_rule_platform_filter': '蚂蚁', 'resolved_platform_name': '蚂蚁花团供应商', 'task_group_id': 'RULE-GROUP-5b8ed8977e8f'}</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-07-23T00:37:00</t>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>{'listing_trace': ['matched:LIST-蚂蚁B级下架:set_offline-&gt;set_offline'], 'platform_observation': {'observed_price': '10.50', 'observed_inventory': 1}, 'listing_target_default_source': 'platform_snapshot', 'generation_mode': 'single_rule', 'selected_rule_type': 'listing', 'selected_rule_id': 'LIST-蚂蚁B级下架', 'selected_rule_platform_filter': '蚂蚁', 'resolved_platform_name': '蚂蚁花团供应商', 'task_group_id': 'RULE-GROUP-02d9b44bf6c1'}</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-07-27T18:54:00</t>
         </is>
       </c>
     </row>
